--- a/Copy of Practice File for Excel for Beginners - ABUBAKARSODEEQ.xlsx
+++ b/Copy of Practice File for Excel for Beginners - ABUBAKARSODEEQ.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M&amp;E UNIT\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M&amp;E UNIT\Downloads\implementation Status\GIT\Intro_Excel_AbubakarSodeeqSuleiman.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -391,22 +391,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -430,13 +414,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Sheet1-style" pivot="0" count="4">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -478,8 +478,23 @@
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>Summary Chart</a:t>
+              <a:t>Employee</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> Net Pay Chart</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="757575"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2837,11 +2852,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="-2012114624"/>
-        <c:axId val="-2012120064"/>
+        <c:axId val="-1549250112"/>
+        <c:axId val="-1549246304"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="-2012114624"/>
+        <c:axId val="-1549250112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2895,7 +2910,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-2012120064"/>
+        <c:crossAx val="-1549246304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2903,7 +2918,7 @@
         <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-2012120064"/>
+        <c:axId val="-1549246304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2969,7 +2984,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-2012114624"/>
+        <c:crossAx val="-1549250112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3010,10 +3025,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4219575" cy="2314575"/>
     <xdr:graphicFrame macro="">
